--- a/artfynd/A 24547-2026 artfynd.xlsx
+++ b/artfynd/A 24547-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>95209928</v>
       </c>
       <c r="B2" t="n">
-        <v>88901</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368756.2420720679</v>
+        <v>368756</v>
       </c>
       <c r="R2" t="n">
-        <v>6591402.263428715</v>
+        <v>6591403</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>

--- a/artfynd/A 24547-2026 artfynd.xlsx
+++ b/artfynd/A 24547-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,9 +798,134 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135775366</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57891</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SV Högliden, Stömne, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>368625</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6591744</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stavnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Peter Adén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Peter Adén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135775366</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24547-2026 artfynd.xlsx
+++ b/artfynd/A 24547-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>135775366</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24547-2026 artfynd.xlsx
+++ b/artfynd/A 24547-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>135775366</v>
       </c>
       <c r="B3" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24547-2026 artfynd.xlsx
+++ b/artfynd/A 24547-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>135775366</v>
       </c>
       <c r="B3" t="n">
-        <v>57894</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24547-2026 artfynd.xlsx
+++ b/artfynd/A 24547-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>135775366</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24547-2026 artfynd.xlsx
+++ b/artfynd/A 24547-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>135775366</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
